--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486691_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486691_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2904</v>
+        <v>6.1691</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3177</v>
+        <v>4.2212</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9727</v>
+        <v>1.9479</v>
       </c>
       <c r="G2" t="n">
         <v>3.8175</v>
@@ -610,13 +610,13 @@
         <v>0.9654</v>
       </c>
       <c r="S2" t="n">
-        <v>1.859</v>
+        <v>1.7377</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0753</v>
+        <v>0.9788</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7589</v>
       </c>
       <c r="V2" t="n">
         <v>0.6138</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6345</v>
+        <v>5.9207</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9764</v>
+        <v>2.8807</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3419</v>
+        <v>3.0399</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5068</v>
+        <v>2.5507</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3245</v>
+        <v>0.3036</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1823</v>
+        <v>2.2471</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6113</v>
+        <v>1.8972</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1871</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4242</v>
+        <v>1.7996</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1045</v>
+        <v>0.6535</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1374</v>
+        <v>0.206</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.242</v>
+        <v>0.4475</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3515</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0892</v>
+        <v>-2.1239</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9346</v>
+        <v>2.1929</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4544</v>
+        <v>1.3511</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4803</v>
+        <v>0.8418</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.4554</v>
+        <v>1.7563</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.7563</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9581</v>
+        <v>4.5962</v>
       </c>
       <c r="E4" t="n">
-        <v>1.943</v>
+        <v>4.8388</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0151</v>
+        <v>-0.2426</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5507</v>
+        <v>6.5068</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3036</v>
+        <v>5.3245</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2471</v>
+        <v>1.1823</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8972</v>
+        <v>6.6113</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09760000000000001</v>
+        <v>5.1871</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7996</v>
+        <v>1.4242</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6535</v>
+        <v>-0.1045</v>
       </c>
       <c r="N4" t="n">
-        <v>0.206</v>
+        <v>0.1374</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4475</v>
+        <v>-0.242</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5792</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1239</v>
+        <v>-3.0892</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2303</v>
+        <v>1.8963</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4133</v>
+        <v>1.3167</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.5796</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7563</v>
+        <v>-2.4554</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7563</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0894</v>
+        <v>3.7458</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1054</v>
+        <v>1.2088</v>
       </c>
       <c r="F5" t="n">
-        <v>2.984</v>
+        <v>2.537</v>
       </c>
       <c r="G5" t="n">
         <v>0.732</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7435</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1928</v>
+        <v>0.2963</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5507</v>
+        <v>1.1037</v>
       </c>
       <c r="V5" t="n">
         <v>1.2277</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2166</v>
+        <v>3.2738</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8142</v>
+        <v>0.7849</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5976</v>
+        <v>2.4889</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6005</v>
+        <v>1.998</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9517</v>
+        <v>0.7931</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6488</v>
+        <v>1.2049</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7388</v>
+        <v>0.9438</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7449</v>
+        <v>0.4486</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9939</v>
+        <v>0.4952</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1384</v>
+        <v>1.0543</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2068</v>
+        <v>0.3445</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3451</v>
+        <v>0.7098</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1954</v>
+        <v>0.3104</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0408</v>
+        <v>-0.1588</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1546</v>
+        <v>0.4692</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9084</v>
+        <v>2.8622</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4195</v>
+        <v>1.9117</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4889</v>
+        <v>0.9505</v>
       </c>
       <c r="G7" t="n">
-        <v>1.998</v>
+        <v>0.1314</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7931</v>
+        <v>0.1584</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2049</v>
+        <v>-0.0271</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9438</v>
+        <v>0.5876</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4486</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4952</v>
+        <v>-0.192</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0543</v>
+        <v>-0.4563</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3445</v>
+        <v>-0.6212</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7098</v>
+        <v>0.165</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0551</v>
+        <v>1.5378</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5243</v>
+        <v>0.4479</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4692</v>
+        <v>1.0898</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7004</v>
+        <v>2.1517</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0476</v>
+        <v>-0.8198</v>
       </c>
       <c r="F8" t="n">
-        <v>2.748</v>
+        <v>2.9715</v>
       </c>
       <c r="G8" t="n">
         <v>1.4661</v>
@@ -1078,13 +1078,13 @@
         <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>1.528</v>
+        <v>0.9792</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6545</v>
+        <v>0.8823</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1266</v>
+        <v>0.0969</v>
       </c>
       <c r="V8" t="n">
         <v>0.2856</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9589</v>
+        <v>2.0004</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1326</v>
+        <v>2.5732</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8263</v>
+        <v>-0.5728</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1314</v>
+        <v>1.6005</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1584</v>
+        <v>0.9517</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0271</v>
+        <v>0.6488</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5876</v>
+        <v>2.7388</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7449</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.192</v>
+        <v>1.9939</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4563</v>
+        <v>-1.1384</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6212</v>
+        <v>0.2068</v>
       </c>
       <c r="O9" t="n">
-        <v>0.165</v>
+        <v>-1.3451</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5792</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6345</v>
+        <v>0.9791</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3312</v>
+        <v>0.7997</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9657</v>
+        <v>0.1794</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2008</v>
+        <v>1.3278</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3564</v>
+        <v>0.2599</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8443000000000001</v>
+        <v>1.0678</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6235000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4728</v>
+        <v>1.5998</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0753</v>
+        <v>0.9788</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3975</v>
+        <v>0.621</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6138</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4904</v>
+        <v>0.1074</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3129</v>
+        <v>0.5979</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8226</v>
+        <v>-0.4905</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6932</v>
+        <v>1.1006</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0964</v>
+        <v>2.4208</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5969</v>
+        <v>-1.3203</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1542</v>
+        <v>1.8256</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.889</v>
+        <v>2.3523</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7347</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.539</v>
+        <v>-0.725</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2074</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3316</v>
+        <v>-0.7935</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7723</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>-2.1239</v>
       </c>
       <c r="R11" t="n">
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9752</v>
+        <v>1.1999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7721</v>
+        <v>0.8962</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2031</v>
+        <v>0.3037</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0262</v>
+        <v>-0.1623</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4363</v>
+        <v>-0.6372</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5899</v>
+        <v>0.4749</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1006</v>
+        <v>-1.6932</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4208</v>
+        <v>-1.0964</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3203</v>
+        <v>-0.5969</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8256</v>
+        <v>-0.1542</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3523</v>
+        <v>-0.889</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0.7347</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.725</v>
+        <v>-1.539</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.2074</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7935</v>
+        <v>-1.3316</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9654</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1239</v>
+        <v>-1.9308</v>
       </c>
       <c r="R12" t="n">
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0663</v>
+        <v>2.3032</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.138</v>
+        <v>1.4478</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2044</v>
+        <v>0.8554</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.4409</v>
+        <v>31.9928</v>
       </c>
       <c r="E13" t="n">
-        <v>17.2684</v>
+        <v>17.8201</v>
       </c>
       <c r="F13" t="n">
         <v>14.1725</v>
@@ -1468,13 +1468,13 @@
         <v>13.5155</v>
       </c>
       <c r="S13" t="n">
-        <v>15.5845</v>
+        <v>16.1363</v>
       </c>
       <c r="T13" t="n">
-        <v>8.685</v>
+        <v>9.236799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>6.899699999999999</v>
+        <v>6.8994</v>
       </c>
       <c r="V13" t="n">
         <v>0.2002999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. JURAN HRVATSKO</t>
+          <t>J. FERMIN DE LUNA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.1248</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4759</v>
+        <v>1.2697</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.468</v>
+        <v>-1.3945</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0001</v>
+        <v>0.9712</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8072</v>
+        <v>-2.2073</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8071</v>
+        <v>3.1785</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3658</v>
+        <v>3.2074</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0207</v>
+        <v>-0.62</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3451</v>
+        <v>3.8274</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3659</v>
+        <v>-2.2362</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8278</v>
+        <v>-1.5873</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5381</v>
+        <v>-0.6489</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1931</v>
+        <v>-3.2823</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9654</v>
+        <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4634</v>
+        <v>-2.3929</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3032</v>
+        <v>-1.1107</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1601</v>
+        <v>-1.2822</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2277</v>
+        <v>2.4554</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FERMIN DE LUNA</t>
+          <t>P. JURAN HRVATSKO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6393</v>
+        <v>-0.5796</v>
       </c>
       <c r="E15" t="n">
-        <v>1.58</v>
+        <v>1.0623</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2193</v>
+        <v>-1.6419</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9712</v>
+        <v>-0.0001</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2073</v>
+        <v>-0.8072</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1785</v>
+        <v>0.8071</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2074</v>
+        <v>1.3658</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.62</v>
+        <v>0.0207</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8274</v>
+        <v>1.3451</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2362</v>
+        <v>-1.3659</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5873</v>
+        <v>-0.8278</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6489</v>
+        <v>-0.5381</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2823</v>
+        <v>-0.1931</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.9074</v>
+        <v>-0.1242</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8004</v>
+        <v>-0.1105</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.1069</v>
+        <v>-0.0137</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4554</v>
+        <v>-1.2277</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9759</v>
+        <v>-0.6008</v>
       </c>
       <c r="E16" t="n">
         <v>1.647</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.623</v>
+        <v>-2.2479</v>
       </c>
       <c r="G16" t="n">
         <v>1.5567</v>
@@ -1702,13 +1702,13 @@
         <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5061</v>
+        <v>-1.1309</v>
       </c>
       <c r="T16" t="n">
         <v>-0.6622</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8439</v>
+        <v>-0.4688</v>
       </c>
       <c r="V16" t="n">
         <v>-1.7989</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7331</v>
+        <v>-0.7967</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2339</v>
+        <v>-0.9237</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4991</v>
+        <v>0.1269</v>
       </c>
       <c r="G17" t="n">
         <v>0.8954</v>
@@ -1780,13 +1780,13 @@
         <v>2.1239</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.1498</v>
+        <v>-2.2135</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3244</v>
+        <v>-1.0141</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.8255</v>
+        <v>-1.1994</v>
       </c>
       <c r="V17" t="n">
         <v>0.3282</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SIBENIK</t>
+          <t>D. SOTO MADRIGAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8599</v>
+        <v>-1.5773</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3265</v>
+        <v>-1.225</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5334</v>
+        <v>-0.3523</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1758</v>
+        <v>-1.5911</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8413</v>
+        <v>-0.0968</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3345</v>
+        <v>-1.4943</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9978</v>
+        <v>-0.7145</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.6622</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4591</v>
+        <v>-1.3767</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1736</v>
+        <v>-0.8766</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3801</v>
+        <v>-0.759</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7935</v>
+        <v>-0.1176</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1239</v>
+        <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8426</v>
+        <v>0.0138</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.359</v>
+        <v>-0.3174</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4836</v>
+        <v>0.3312</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SOTO MADRIGAL</t>
+          <t>L. SIBENIK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9221</v>
+        <v>-1.8792</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4319</v>
+        <v>-0.5334</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4902</v>
+        <v>-1.3458</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5911</v>
+        <v>-1.1758</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0968</v>
+        <v>-0.8413</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4943</v>
+        <v>-0.3345</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7145</v>
+        <v>0.9978</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6622</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3767</v>
+        <v>0.4591</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8766</v>
+        <v>-2.1736</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.759</v>
+        <v>-1.3801</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1176</v>
+        <v>-0.7935</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1931</v>
+        <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.331</v>
+        <v>-1.8619</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5243</v>
+        <v>-0.5658</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1933</v>
+        <v>-1.2961</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1124</v>
+        <v>-2.6006</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7038</v>
+        <v>-2.1175</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4085</v>
+        <v>-0.483</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5591</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6398</v>
+        <v>0.1516</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4963</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1435</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VILLANUEVA CUBELO</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8816</v>
+        <v>-2.8337</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0531</v>
+        <v>0.0711</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8285</v>
+        <v>-2.9048</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4844</v>
+        <v>-1.3165</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7037</v>
+        <v>-0.4348</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2193</v>
+        <v>-0.8817</v>
       </c>
       <c r="J21" t="n">
-        <v>0.289</v>
+        <v>0.9056</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3658</v>
+        <v>0.0488</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.8568</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7734</v>
+        <v>-2.2222</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0695</v>
+        <v>-0.4837</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2961</v>
+        <v>-1.7385</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7723</v>
+        <v>2.3169</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3971</v>
+        <v>-2.0618</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8554</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4582</v>
+        <v>-1.1581</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6138</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3282</v>
+        <v>1.2277</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2856</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>M. VILLANUEVA CUBELO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4087</v>
+        <v>-2.8982</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2392</v>
+        <v>-1.8462</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1695</v>
+        <v>-1.052</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3165</v>
+        <v>-1.4844</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4348</v>
+        <v>-1.7037</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8817</v>
+        <v>0.2193</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9056</v>
+        <v>0.289</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0488</v>
+        <v>0.3658</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8568</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2222</v>
+        <v>-1.7734</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4837</v>
+        <v>-2.0695</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7385</v>
+        <v>0.2961</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3169</v>
+        <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.6368</v>
+        <v>-0.4138</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.214</v>
+        <v>-0.6485</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4227</v>
+        <v>0.2348</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6138</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2277</v>
+        <v>-0.3282</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8415</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3395</v>
+        <v>-4.1189</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5319</v>
+        <v>-3.325</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8076</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-4.3671</v>
@@ -2248,13 +2248,13 @@
         <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3586</v>
+        <v>-0.138</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.745</v>
+        <v>-0.5382</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3865</v>
+        <v>0.4002</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4922</v>
+        <v>-4.4714</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6983</v>
+        <v>-2.8017</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7939</v>
+        <v>-1.6697</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2989</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5794</v>
+        <v>-0.5587</v>
       </c>
       <c r="T24" t="n">
-        <v>0.11</v>
+        <v>0.0066</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6894</v>
+        <v>-0.5653</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.0843</v>
+        <v>-6.2017</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6569</v>
+        <v>-5.4501</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4274</v>
+        <v>-0.7517</v>
       </c>
       <c r="G25" t="n">
         <v>-4.2172</v>
@@ -2404,13 +2404,13 @@
         <v>1.9308</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.9789</v>
+        <v>-2.0964</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3244</v>
+        <v>-1.1175</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6546</v>
+        <v>-0.9788</v>
       </c>
       <c r="V25" t="n">
         <v>1.2703</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-31.4411</v>
+        <v>-28.6829</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.1726</v>
+        <v>-14.1725</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.2684</v>
+        <v>-14.5106</v>
       </c>
       <c r="G26" t="n">
         <v>-17.5869</v>
@@ -2473,7 +2473,7 @@
         <v>-5.867</v>
       </c>
       <c r="P26" t="n">
-        <v>1.930800000000001</v>
+        <v>1.9308</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.5156</v>
@@ -2482,13 +2482,13 @@
         <v>15.4463</v>
       </c>
       <c r="S26" t="n">
-        <v>-15.5845</v>
+        <v>-12.8267</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.8996</v>
+        <v>-6.8994</v>
       </c>
       <c r="U26" t="n">
-        <v>-8.685</v>
+        <v>-5.9272</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2002999999999999</v>
